--- a/readme.xlsx
+++ b/readme.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\tsk_code\web_ban_hang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45987B5-7D5B-4AD4-87FE-C154C7C8B706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1A0656-A394-4B58-822A-BEB4F6DB7C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prompt_AI" sheetId="1" r:id="rId1"/>
     <sheet name="Result" sheetId="2" r:id="rId2"/>
     <sheet name="Test" sheetId="3" r:id="rId3"/>
     <sheet name="history_log" sheetId="4" r:id="rId4"/>
+    <sheet name="Make_online" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>code tao website them gio hang</t>
   </si>
@@ -391,13 +392,297 @@
   </si>
   <si>
     <t>Add opne lienhe.html to Javascript</t>
+  </si>
+  <si>
+    <t>Option 2: Host via GitHub Pages (Most Professional)</t>
+  </si>
+  <si>
+    <t>This is the industry standard for developers. It keeps your code saved online and updates your site automatically. [1]</t>
+  </si>
+  <si>
+    <t>1. Create a free account on ⁠GitHub.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>New</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to create a repository. Name it anything you like (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>my-first-webpage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Make sure it is set to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>uploading an existing file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Drag and drop your </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>index.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> file into the box, then click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Commit changes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Go to the repository </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Settings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab → click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pages</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> on the left menu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Under "Build and deployment", change the Source branch from </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (or </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>master</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) and click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. Wait 1–2 minutes. Refresh the page to see your live URL (usually </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>yourusername.github.io/repository-name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>). [1, 2, 3]</t>
+    </r>
+  </si>
+  <si>
+    <t>giyhub account tminhluu8</t>
+  </si>
+  <si>
+    <t>tminhluu8-design</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +722,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -459,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -480,6 +785,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1011,4 +1322,66 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6643769-AE25-41B6-A26E-8EB92D489BAC}">
+  <dimension ref="C2:F11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C4" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C11" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://www.youtube.com/watch?v=p1QU3kLFPdg&amp;t=81" xr:uid="{85A54429-BF77-4698-B4A3-8F44391796FB}"/>
+    <hyperlink ref="C6" r:id="rId2" display="https://github.com/" xr:uid="{829B6932-0AE9-494C-97B9-F28C7AAF6A37}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>